--- a/benchmark_results.xlsx
+++ b/benchmark_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AALB\Desktop\mp\graph\graphxmaf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F33444-1A6A-4707-B43C-1E2687E73AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8EBE19-1A9E-4D7B-AC16-083BD5DFF68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Graph" sheetId="1" r:id="rId1"/>
@@ -16034,11 +16034,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -26074,7 +26075,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:U45"/>
+  <dimension ref="A1:U46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -27389,68 +27390,6 @@
         <v>761</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>762</v>
-      </c>
-      <c r="B24" t="s">
-        <v>763</v>
-      </c>
-      <c r="C24" t="s">
-        <v>609</v>
-      </c>
-      <c r="D24" t="s">
-        <v>610</v>
-      </c>
-      <c r="E24" t="s">
-        <v>23</v>
-      </c>
-      <c r="F24" t="s">
-        <v>611</v>
-      </c>
-      <c r="G24" t="s">
-        <v>612</v>
-      </c>
-      <c r="H24" t="s">
-        <v>764</v>
-      </c>
-      <c r="I24">
-        <v>43.844999999999999</v>
-      </c>
-      <c r="J24">
-        <v>7155</v>
-      </c>
-      <c r="K24">
-        <v>4101</v>
-      </c>
-      <c r="L24">
-        <v>11256</v>
-      </c>
-      <c r="M24">
-        <v>13241</v>
-      </c>
-      <c r="N24">
-        <v>3</v>
-      </c>
-      <c r="O24" t="s">
-        <v>614</v>
-      </c>
-      <c r="P24" t="s">
-        <v>765</v>
-      </c>
-      <c r="Q24" t="b">
-        <v>1</v>
-      </c>
-      <c r="S24" t="s">
-        <v>616</v>
-      </c>
-      <c r="T24">
-        <v>1</v>
-      </c>
-      <c r="U24" t="s">
-        <v>766</v>
-      </c>
-    </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>762</v>
@@ -27459,58 +27398,58 @@
         <v>763</v>
       </c>
       <c r="C25" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="D25" t="s">
         <v>610</v>
       </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F25" t="s">
         <v>611</v>
       </c>
       <c r="G25" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="H25" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="I25">
-        <v>8.3580000000000005</v>
+        <v>43.844999999999999</v>
       </c>
       <c r="J25">
-        <v>3803</v>
+        <v>7155</v>
       </c>
       <c r="K25">
-        <v>665</v>
+        <v>4101</v>
       </c>
       <c r="L25">
-        <v>4468</v>
+        <v>11256</v>
       </c>
       <c r="M25">
-        <v>2161</v>
+        <v>13241</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O25" t="s">
-        <v>768</v>
+        <v>614</v>
       </c>
       <c r="P25" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="Q25" t="b">
         <v>1</v>
       </c>
       <c r="S25" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="T25">
         <v>1</v>
       </c>
       <c r="U25" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -27521,7 +27460,7 @@
         <v>763</v>
       </c>
       <c r="C26" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="D26" t="s">
         <v>610</v>
@@ -27533,46 +27472,46 @@
         <v>611</v>
       </c>
       <c r="G26" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="H26" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="I26">
-        <v>29.023</v>
+        <v>8.3580000000000005</v>
       </c>
       <c r="J26">
-        <v>5828</v>
+        <v>3803</v>
       </c>
       <c r="K26">
-        <v>2744</v>
+        <v>665</v>
       </c>
       <c r="L26">
-        <v>8572</v>
+        <v>4468</v>
       </c>
       <c r="M26">
-        <v>8790</v>
+        <v>2161</v>
       </c>
       <c r="N26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O26" t="s">
-        <v>626</v>
+        <v>768</v>
       </c>
       <c r="P26" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="Q26" t="b">
         <v>1</v>
       </c>
       <c r="S26" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="T26">
         <v>1</v>
       </c>
       <c r="U26" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -27583,58 +27522,58 @@
         <v>763</v>
       </c>
       <c r="C27" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="D27" t="s">
         <v>610</v>
       </c>
       <c r="E27" t="s">
-        <v>185</v>
+        <v>31</v>
       </c>
       <c r="F27" t="s">
-        <v>630</v>
+        <v>611</v>
       </c>
       <c r="G27" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="H27" t="s">
-        <v>632</v>
+        <v>771</v>
       </c>
       <c r="I27">
-        <v>9.8620000000000001</v>
+        <v>29.023</v>
       </c>
       <c r="J27">
-        <v>7852</v>
+        <v>5828</v>
       </c>
       <c r="K27">
-        <v>642</v>
+        <v>2744</v>
       </c>
       <c r="L27">
-        <v>8494</v>
+        <v>8572</v>
       </c>
       <c r="M27">
-        <v>1777</v>
+        <v>8790</v>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O27" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="P27" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="Q27" t="b">
         <v>1</v>
       </c>
       <c r="S27" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="T27">
         <v>1</v>
       </c>
       <c r="U27" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -27645,58 +27584,58 @@
         <v>763</v>
       </c>
       <c r="C28" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="D28" t="s">
         <v>610</v>
       </c>
       <c r="E28" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="F28" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="G28" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="H28" t="s">
-        <v>776</v>
+        <v>632</v>
       </c>
       <c r="I28">
-        <v>23.202999999999999</v>
+        <v>9.8620000000000001</v>
       </c>
       <c r="J28">
-        <v>6060</v>
+        <v>7852</v>
       </c>
       <c r="K28">
-        <v>2468</v>
+        <v>642</v>
       </c>
       <c r="L28">
-        <v>8528</v>
+        <v>8494</v>
       </c>
       <c r="M28">
-        <v>8861</v>
+        <v>1777</v>
       </c>
       <c r="N28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O28" t="s">
-        <v>777</v>
+        <v>633</v>
       </c>
       <c r="P28" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="Q28" t="b">
         <v>1</v>
       </c>
       <c r="S28" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="T28">
         <v>1</v>
       </c>
       <c r="U28" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -27707,7 +27646,7 @@
         <v>763</v>
       </c>
       <c r="C29" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="D29" t="s">
         <v>610</v>
@@ -27716,49 +27655,49 @@
         <v>23</v>
       </c>
       <c r="F29" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="G29" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="H29" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="I29">
-        <v>13.904</v>
+        <v>23.202999999999999</v>
       </c>
       <c r="J29">
-        <v>8920</v>
+        <v>6060</v>
       </c>
       <c r="K29">
-        <v>1443</v>
+        <v>2468</v>
       </c>
       <c r="L29">
-        <v>10363</v>
+        <v>8528</v>
       </c>
       <c r="M29">
-        <v>5690</v>
+        <v>8861</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29" t="s">
-        <v>647</v>
+        <v>777</v>
       </c>
       <c r="P29" t="s">
-        <v>648</v>
+        <v>778</v>
       </c>
       <c r="Q29" t="b">
         <v>1</v>
       </c>
       <c r="S29" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="T29">
         <v>1</v>
       </c>
       <c r="U29" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -27769,7 +27708,7 @@
         <v>763</v>
       </c>
       <c r="C30" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="D30" t="s">
         <v>610</v>
@@ -27778,49 +27717,49 @@
         <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="G30" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="H30" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="I30">
-        <v>7.85</v>
+        <v>13.904</v>
       </c>
       <c r="J30">
-        <v>4113</v>
+        <v>8920</v>
       </c>
       <c r="K30">
-        <v>649</v>
+        <v>1443</v>
       </c>
       <c r="L30">
-        <v>4762</v>
+        <v>10363</v>
       </c>
       <c r="M30">
-        <v>2093</v>
+        <v>5690</v>
       </c>
       <c r="N30">
         <v>5</v>
       </c>
       <c r="O30" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="P30" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="Q30" t="b">
         <v>1</v>
       </c>
       <c r="S30" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="T30">
         <v>1</v>
       </c>
       <c r="U30" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -27831,58 +27770,58 @@
         <v>763</v>
       </c>
       <c r="C31" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="D31" t="s">
-        <v>658</v>
+        <v>610</v>
       </c>
       <c r="E31" t="s">
         <v>23</v>
       </c>
       <c r="F31" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="G31" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="H31" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="I31">
-        <v>5.3010000000000002</v>
+        <v>7.85</v>
       </c>
       <c r="J31">
-        <v>3444</v>
+        <v>4113</v>
       </c>
       <c r="K31">
-        <v>388</v>
+        <v>649</v>
       </c>
       <c r="L31">
-        <v>3832</v>
+        <v>4762</v>
       </c>
       <c r="M31">
-        <v>1066</v>
+        <v>2093</v>
       </c>
       <c r="N31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O31" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="P31" t="s">
-        <v>785</v>
+        <v>655</v>
       </c>
       <c r="Q31" t="b">
         <v>1</v>
       </c>
       <c r="S31" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="T31">
         <v>1</v>
       </c>
       <c r="U31" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -27893,58 +27832,58 @@
         <v>763</v>
       </c>
       <c r="C32" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="D32" t="s">
         <v>658</v>
       </c>
       <c r="E32" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F32" t="s">
         <v>659</v>
       </c>
       <c r="G32" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="H32" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="I32">
-        <v>6.83</v>
+        <v>5.3010000000000002</v>
       </c>
       <c r="J32">
-        <v>3585</v>
+        <v>3444</v>
       </c>
       <c r="K32">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L32">
-        <v>3974</v>
+        <v>3832</v>
       </c>
       <c r="M32">
         <v>1066</v>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O32" t="s">
-        <v>788</v>
+        <v>662</v>
       </c>
       <c r="P32" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="Q32" t="b">
         <v>1</v>
       </c>
       <c r="S32" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="T32">
         <v>1</v>
       </c>
       <c r="U32" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -27955,58 +27894,58 @@
         <v>763</v>
       </c>
       <c r="C33" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="D33" t="s">
         <v>658</v>
       </c>
       <c r="E33" t="s">
-        <v>185</v>
+        <v>31</v>
       </c>
       <c r="F33" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="G33" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="H33" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="I33">
-        <v>9.1289999999999996</v>
+        <v>6.83</v>
       </c>
       <c r="J33">
-        <v>4260</v>
+        <v>3585</v>
       </c>
       <c r="K33">
-        <v>457</v>
+        <v>389</v>
       </c>
       <c r="L33">
-        <v>4717</v>
+        <v>3974</v>
       </c>
       <c r="M33">
-        <v>1293</v>
+        <v>1066</v>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O33" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="P33" t="s">
-        <v>676</v>
+        <v>789</v>
       </c>
       <c r="Q33" t="b">
         <v>1</v>
       </c>
       <c r="S33" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="T33">
         <v>1</v>
       </c>
       <c r="U33" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -28017,58 +27956,58 @@
         <v>763</v>
       </c>
       <c r="C34" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="D34" t="s">
         <v>658</v>
       </c>
       <c r="E34" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="F34" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="G34" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="H34" t="s">
-        <v>681</v>
+        <v>791</v>
       </c>
       <c r="I34">
-        <v>16.983000000000001</v>
+        <v>9.1289999999999996</v>
       </c>
       <c r="J34">
-        <v>5024</v>
+        <v>4260</v>
       </c>
       <c r="K34">
-        <v>1688</v>
+        <v>457</v>
       </c>
       <c r="L34">
-        <v>6712</v>
+        <v>4717</v>
       </c>
       <c r="M34">
-        <v>6644</v>
+        <v>1293</v>
       </c>
       <c r="N34">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O34" t="s">
-        <v>682</v>
+        <v>792</v>
       </c>
       <c r="P34" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="Q34" t="b">
         <v>1</v>
       </c>
       <c r="S34" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="T34">
         <v>1</v>
       </c>
       <c r="U34" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -28079,7 +28018,7 @@
         <v>763</v>
       </c>
       <c r="C35" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="D35" t="s">
         <v>658</v>
@@ -28088,49 +28027,49 @@
         <v>23</v>
       </c>
       <c r="F35" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="G35" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="H35" t="s">
-        <v>795</v>
+        <v>681</v>
       </c>
       <c r="I35">
-        <v>20.449000000000002</v>
+        <v>16.983000000000001</v>
       </c>
       <c r="J35">
-        <v>7005</v>
+        <v>5024</v>
       </c>
       <c r="K35">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="L35">
-        <v>8691</v>
+        <v>6712</v>
       </c>
       <c r="M35">
-        <v>6846</v>
+        <v>6644</v>
       </c>
       <c r="N35">
         <v>5</v>
       </c>
       <c r="O35" t="s">
-        <v>796</v>
+        <v>682</v>
       </c>
       <c r="P35" t="s">
-        <v>797</v>
+        <v>683</v>
       </c>
       <c r="Q35" t="b">
         <v>1</v>
       </c>
       <c r="S35" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="T35">
         <v>1</v>
       </c>
       <c r="U35" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -28141,7 +28080,7 @@
         <v>763</v>
       </c>
       <c r="C36" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="D36" t="s">
         <v>658</v>
@@ -28150,49 +28089,49 @@
         <v>23</v>
       </c>
       <c r="F36" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="G36" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="H36" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="I36">
-        <v>9.9589999999999996</v>
+        <v>20.449000000000002</v>
       </c>
       <c r="J36">
-        <v>3982</v>
+        <v>7005</v>
       </c>
       <c r="K36">
-        <v>756</v>
+        <v>1686</v>
       </c>
       <c r="L36">
-        <v>4738</v>
+        <v>8691</v>
       </c>
       <c r="M36">
-        <v>3057</v>
+        <v>6846</v>
       </c>
       <c r="N36">
         <v>5</v>
       </c>
       <c r="O36" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="P36" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="Q36" t="b">
         <v>1</v>
       </c>
       <c r="S36" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="T36">
         <v>1</v>
       </c>
       <c r="U36" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -28203,58 +28142,58 @@
         <v>763</v>
       </c>
       <c r="C37" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="D37" t="s">
-        <v>700</v>
+        <v>658</v>
       </c>
       <c r="E37" t="s">
         <v>23</v>
       </c>
       <c r="F37" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="G37" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="H37" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="I37">
-        <v>10.37</v>
+        <v>9.9589999999999996</v>
       </c>
       <c r="J37">
-        <v>3919</v>
+        <v>3982</v>
       </c>
       <c r="K37">
-        <v>855</v>
+        <v>756</v>
       </c>
       <c r="L37">
-        <v>4774</v>
+        <v>4738</v>
       </c>
       <c r="M37">
-        <v>2615</v>
+        <v>3057</v>
       </c>
       <c r="N37">
         <v>5</v>
       </c>
       <c r="O37" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="P37" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="Q37" t="b">
         <v>1</v>
       </c>
       <c r="S37" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="T37">
         <v>1</v>
       </c>
       <c r="U37" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -28265,58 +28204,58 @@
         <v>763</v>
       </c>
       <c r="C38" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="D38" t="s">
         <v>700</v>
       </c>
       <c r="E38" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F38" t="s">
         <v>701</v>
       </c>
       <c r="G38" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="H38" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="I38">
-        <v>14.837</v>
+        <v>10.37</v>
       </c>
       <c r="J38">
-        <v>4318</v>
+        <v>3919</v>
       </c>
       <c r="K38">
-        <v>1258</v>
+        <v>855</v>
       </c>
       <c r="L38">
-        <v>5576</v>
+        <v>4774</v>
       </c>
       <c r="M38">
-        <v>4170</v>
+        <v>2615</v>
       </c>
       <c r="N38">
         <v>5</v>
       </c>
       <c r="O38" t="s">
-        <v>710</v>
+        <v>804</v>
       </c>
       <c r="P38" t="s">
-        <v>711</v>
+        <v>805</v>
       </c>
       <c r="Q38" t="b">
         <v>1</v>
       </c>
       <c r="S38" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="T38">
         <v>1</v>
       </c>
       <c r="U38" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -28327,58 +28266,58 @@
         <v>763</v>
       </c>
       <c r="C39" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="D39" t="s">
         <v>700</v>
       </c>
       <c r="E39" t="s">
-        <v>185</v>
+        <v>31</v>
       </c>
       <c r="F39" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="G39" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="H39" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="I39">
-        <v>15.476000000000001</v>
+        <v>14.837</v>
       </c>
       <c r="J39">
-        <v>5140</v>
+        <v>4318</v>
       </c>
       <c r="K39">
-        <v>1165</v>
+        <v>1258</v>
       </c>
       <c r="L39">
-        <v>6305</v>
+        <v>5576</v>
       </c>
       <c r="M39">
-        <v>3506</v>
+        <v>4170</v>
       </c>
       <c r="N39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O39" t="s">
-        <v>810</v>
+        <v>710</v>
       </c>
       <c r="P39" t="s">
-        <v>811</v>
+        <v>711</v>
       </c>
       <c r="Q39" t="b">
         <v>1</v>
       </c>
       <c r="S39" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="T39">
         <v>1</v>
       </c>
       <c r="U39" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -28389,58 +28328,58 @@
         <v>763</v>
       </c>
       <c r="C40" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="D40" t="s">
         <v>700</v>
       </c>
       <c r="E40" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="F40" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="G40" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="H40" t="s">
-        <v>723</v>
+        <v>809</v>
       </c>
       <c r="I40">
-        <v>3.548</v>
+        <v>15.476000000000001</v>
       </c>
       <c r="J40">
-        <v>3179</v>
+        <v>5140</v>
       </c>
       <c r="K40">
-        <v>121</v>
+        <v>1165</v>
       </c>
       <c r="L40">
-        <v>3300</v>
+        <v>6305</v>
       </c>
       <c r="M40">
-        <v>425</v>
+        <v>3506</v>
       </c>
       <c r="N40">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O40" t="s">
-        <v>724</v>
+        <v>810</v>
       </c>
       <c r="P40" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="Q40" t="b">
         <v>1</v>
       </c>
       <c r="S40" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="T40">
         <v>1</v>
       </c>
       <c r="U40" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -28451,7 +28390,7 @@
         <v>763</v>
       </c>
       <c r="C41" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="D41" t="s">
         <v>700</v>
@@ -28460,49 +28399,49 @@
         <v>23</v>
       </c>
       <c r="F41" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="G41" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="H41" t="s">
-        <v>815</v>
+        <v>723</v>
       </c>
       <c r="I41">
-        <v>6.3689999999999998</v>
+        <v>3.548</v>
       </c>
       <c r="J41">
-        <v>3485</v>
+        <v>3179</v>
       </c>
       <c r="K41">
-        <v>417</v>
+        <v>121</v>
       </c>
       <c r="L41">
-        <v>3902</v>
+        <v>3300</v>
       </c>
       <c r="M41">
-        <v>827</v>
+        <v>425</v>
       </c>
       <c r="N41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O41" t="s">
-        <v>816</v>
+        <v>724</v>
       </c>
       <c r="P41" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="Q41" t="b">
         <v>1</v>
       </c>
       <c r="S41" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="T41">
         <v>1</v>
       </c>
       <c r="U41" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -28513,58 +28452,58 @@
         <v>763</v>
       </c>
       <c r="C42" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="D42" t="s">
         <v>700</v>
       </c>
       <c r="E42" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="F42" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="G42" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="H42" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="I42">
-        <v>11.877000000000001</v>
+        <v>6.3689999999999998</v>
       </c>
       <c r="J42">
-        <v>3886</v>
+        <v>3485</v>
       </c>
       <c r="K42">
-        <v>804</v>
+        <v>417</v>
       </c>
       <c r="L42">
-        <v>4690</v>
+        <v>3902</v>
       </c>
       <c r="M42">
-        <v>2836</v>
+        <v>827</v>
       </c>
       <c r="N42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O42" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="P42" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="Q42" t="b">
         <v>1</v>
       </c>
       <c r="S42" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="T42">
         <v>1</v>
       </c>
       <c r="U42" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -28575,58 +28514,58 @@
         <v>763</v>
       </c>
       <c r="C43" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="D43" t="s">
         <v>700</v>
       </c>
       <c r="E43" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
       <c r="F43" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="G43" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="H43" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="I43">
-        <v>12.186</v>
+        <v>11.877000000000001</v>
       </c>
       <c r="J43">
-        <v>5510</v>
+        <v>3886</v>
       </c>
       <c r="K43">
-        <v>1065</v>
+        <v>804</v>
       </c>
       <c r="L43">
-        <v>6575</v>
+        <v>4690</v>
       </c>
       <c r="M43">
-        <v>3750</v>
+        <v>2836</v>
       </c>
       <c r="N43">
         <v>5</v>
       </c>
       <c r="O43" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="P43" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="Q43" t="b">
         <v>1</v>
       </c>
       <c r="S43" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="T43">
         <v>1</v>
       </c>
       <c r="U43" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -28637,7 +28576,7 @@
         <v>763</v>
       </c>
       <c r="C44" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="D44" t="s">
         <v>700</v>
@@ -28646,49 +28585,49 @@
         <v>23</v>
       </c>
       <c r="F44" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="G44" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="H44" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="I44">
-        <v>19.873999999999999</v>
+        <v>12.186</v>
       </c>
       <c r="J44">
-        <v>9412</v>
+        <v>5510</v>
       </c>
       <c r="K44">
-        <v>2182</v>
+        <v>1065</v>
       </c>
       <c r="L44">
-        <v>11594</v>
+        <v>6575</v>
       </c>
       <c r="M44">
-        <v>8499</v>
+        <v>3750</v>
       </c>
       <c r="N44">
         <v>5</v>
       </c>
       <c r="O44" t="s">
-        <v>752</v>
+        <v>824</v>
       </c>
       <c r="P44" t="s">
-        <v>96</v>
+        <v>825</v>
       </c>
       <c r="Q44" t="b">
         <v>1</v>
       </c>
       <c r="S44" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="T44">
         <v>1</v>
       </c>
       <c r="U44" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -28699,7 +28638,7 @@
         <v>763</v>
       </c>
       <c r="C45" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="D45" t="s">
         <v>700</v>
@@ -28708,48 +28647,110 @@
         <v>23</v>
       </c>
       <c r="F45" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="G45" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="H45" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="I45">
-        <v>6.194</v>
+        <v>19.873999999999999</v>
       </c>
       <c r="J45">
-        <v>3862</v>
+        <v>9412</v>
       </c>
       <c r="K45">
-        <v>575</v>
+        <v>2182</v>
       </c>
       <c r="L45">
-        <v>4437</v>
+        <v>11594</v>
       </c>
       <c r="M45">
-        <v>2199</v>
+        <v>8499</v>
       </c>
       <c r="N45">
         <v>5</v>
       </c>
       <c r="O45" t="s">
+        <v>752</v>
+      </c>
+      <c r="P45" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q45" t="b">
+        <v>1</v>
+      </c>
+      <c r="S45" t="s">
+        <v>754</v>
+      </c>
+      <c r="T45">
+        <v>1</v>
+      </c>
+      <c r="U45" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>762</v>
+      </c>
+      <c r="B46" t="s">
+        <v>763</v>
+      </c>
+      <c r="C46" t="s">
+        <v>755</v>
+      </c>
+      <c r="D46" t="s">
+        <v>700</v>
+      </c>
+      <c r="E46" t="s">
+        <v>23</v>
+      </c>
+      <c r="F46" t="s">
+        <v>756</v>
+      </c>
+      <c r="G46" t="s">
+        <v>757</v>
+      </c>
+      <c r="H46" t="s">
+        <v>829</v>
+      </c>
+      <c r="I46">
+        <v>6.194</v>
+      </c>
+      <c r="J46">
+        <v>3862</v>
+      </c>
+      <c r="K46">
+        <v>575</v>
+      </c>
+      <c r="L46">
+        <v>4437</v>
+      </c>
+      <c r="M46">
+        <v>2199</v>
+      </c>
+      <c r="N46">
+        <v>5</v>
+      </c>
+      <c r="O46" t="s">
         <v>759</v>
       </c>
-      <c r="P45" t="s">
+      <c r="P46" t="s">
         <v>760</v>
       </c>
-      <c r="Q45" t="b">
-        <v>1</v>
-      </c>
-      <c r="S45" t="s">
+      <c r="Q46" t="b">
+        <v>1</v>
+      </c>
+      <c r="S46" t="s">
         <v>761</v>
       </c>
-      <c r="T45">
-        <v>1</v>
-      </c>
-      <c r="U45" t="s">
+      <c r="T46">
+        <v>1</v>
+      </c>
+      <c r="U46" t="s">
         <v>830</v>
       </c>
     </row>
@@ -28760,12 +28761,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="80" customWidth="1"/>
+    <col min="3" max="3" width="142" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="56" customWidth="1"/>
@@ -29029,376 +29030,314 @@
         <v>855</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>831</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>832</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
         <v>856</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>857</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="4" t="s">
         <v>858</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="4" t="s">
         <v>859</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="4" t="s">
         <v>860</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="4">
         <v>9.7680000000000007</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="4">
         <v>1145</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="4">
         <v>145</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="4">
         <v>1290</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="4">
         <v>469</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="4">
         <v>3</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O5" s="4" t="s">
         <v>861</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5" s="4" t="s">
         <v>862</v>
       </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" t="s">
+      <c r="Q5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S5" s="4" t="s">
         <v>863</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="4">
         <v>5</v>
       </c>
-      <c r="U5" t="s">
+      <c r="U5" s="4" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="6" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>831</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>832</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
         <v>865</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>857</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="4" t="s">
         <v>858</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="4" t="s">
         <v>866</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="4" t="s">
         <v>867</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="4">
         <v>22.012</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="4">
         <v>1669</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="4">
         <v>243</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="4">
         <v>1912</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="4">
         <v>752</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="4">
         <v>5</v>
       </c>
-      <c r="O6" t="s">
+      <c r="O6" s="4" t="s">
         <v>868</v>
       </c>
-      <c r="P6" t="s">
+      <c r="P6" s="4" t="s">
         <v>869</v>
       </c>
-      <c r="Q6" t="b">
-        <v>1</v>
-      </c>
-      <c r="S6" t="s">
+      <c r="Q6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S6" s="4" t="s">
         <v>870</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="4">
         <v>5</v>
       </c>
-      <c r="U6" t="s">
+      <c r="U6" s="4" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="2" t="s">
         <v>873</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>12.863</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>1747</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="2">
         <v>240</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="2">
         <v>1987</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="2">
         <v>814</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="2">
         <v>4</v>
       </c>
-      <c r="O7" t="s">
+      <c r="O7" s="2" t="s">
         <v>876</v>
       </c>
-      <c r="P7" t="s">
+      <c r="P7" s="2" t="s">
         <v>877</v>
       </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="S7" t="s">
+      <c r="Q7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S7" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="2">
         <v>5</v>
       </c>
-      <c r="U7" t="s">
+      <c r="U7" s="2" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="2" t="s">
         <v>858</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="2" t="s">
         <v>881</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="2" t="s">
         <v>882</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>30.151</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>1802</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <v>653</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="2">
         <v>2455</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="2">
         <v>1663</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="2">
         <v>5</v>
       </c>
-      <c r="O8" t="s">
+      <c r="O8" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="P8" t="s">
+      <c r="P8" s="2" t="s">
         <v>884</v>
       </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-      <c r="S8" t="s">
+      <c r="Q8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S8" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="2">
         <v>4</v>
       </c>
-      <c r="U8" t="s">
+      <c r="U8" s="2" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>887</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="2" t="s">
         <v>888</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="2" t="s">
         <v>889</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>27.428999999999998</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="2">
         <v>3183</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="2">
         <v>232</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="2">
         <v>3415</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="2">
         <v>807</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="2">
         <v>3</v>
       </c>
-      <c r="O9" t="s">
+      <c r="O9" s="2" t="s">
         <v>891</v>
       </c>
-      <c r="P9" t="s">
+      <c r="P9" s="2" t="s">
         <v>892</v>
       </c>
-      <c r="Q9" t="b">
-        <v>1</v>
-      </c>
-      <c r="S9" t="s">
+      <c r="Q9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S9" s="2" t="s">
         <v>893</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="2">
         <v>5</v>
       </c>
-      <c r="U9" t="s">
+      <c r="U9" s="2" t="s">
         <v>894</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>895</v>
-      </c>
-      <c r="B10" t="s">
-        <v>896</v>
-      </c>
-      <c r="C10" t="s">
-        <v>412</v>
-      </c>
-      <c r="D10" t="s">
-        <v>833</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" t="s">
-        <v>834</v>
-      </c>
-      <c r="G10" t="s">
-        <v>835</v>
-      </c>
-      <c r="H10" t="s">
-        <v>897</v>
-      </c>
-      <c r="I10">
-        <v>8.1010000000000009</v>
-      </c>
-      <c r="J10">
-        <v>742</v>
-      </c>
-      <c r="K10">
-        <v>35</v>
-      </c>
-      <c r="L10">
-        <v>777</v>
-      </c>
-      <c r="M10">
-        <v>131</v>
-      </c>
-      <c r="N10">
-        <v>5</v>
-      </c>
-      <c r="O10" t="s">
-        <v>837</v>
-      </c>
-      <c r="P10" t="s">
-        <v>838</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-      <c r="S10" t="s">
-        <v>898</v>
-      </c>
-      <c r="T10">
-        <v>5</v>
-      </c>
-      <c r="U10" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -29409,10 +29348,10 @@
         <v>896</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>412</v>
       </c>
       <c r="D11" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="E11" t="s">
         <v>23</v>
@@ -29421,46 +29360,46 @@
         <v>834</v>
       </c>
       <c r="G11" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="H11" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="I11">
-        <v>10.667999999999999</v>
+        <v>8.1010000000000009</v>
       </c>
       <c r="J11">
-        <v>941</v>
+        <v>742</v>
       </c>
       <c r="K11">
-        <v>201</v>
+        <v>35</v>
       </c>
       <c r="L11">
-        <v>1142</v>
+        <v>777</v>
       </c>
       <c r="M11">
-        <v>722</v>
+        <v>131</v>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O11" t="s">
-        <v>901</v>
+        <v>837</v>
       </c>
       <c r="P11" t="s">
-        <v>902</v>
+        <v>838</v>
       </c>
       <c r="Q11" t="b">
         <v>1</v>
       </c>
       <c r="S11" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="T11">
         <v>5</v>
       </c>
       <c r="U11" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -29471,10 +29410,10 @@
         <v>896</v>
       </c>
       <c r="C12" t="s">
-        <v>848</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="E12" t="s">
         <v>23</v>
@@ -29483,46 +29422,46 @@
         <v>834</v>
       </c>
       <c r="G12" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="H12" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="I12">
-        <v>46.625</v>
+        <v>10.667999999999999</v>
       </c>
       <c r="J12">
-        <v>4810</v>
+        <v>941</v>
       </c>
       <c r="K12">
-        <v>577</v>
+        <v>201</v>
       </c>
       <c r="L12">
-        <v>5387</v>
+        <v>1142</v>
       </c>
       <c r="M12">
-        <v>1542</v>
+        <v>722</v>
       </c>
       <c r="N12">
         <v>2</v>
       </c>
       <c r="O12" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="P12" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="Q12" t="b">
         <v>1</v>
       </c>
       <c r="S12" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="T12">
         <v>5</v>
       </c>
       <c r="U12" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -29533,58 +29472,58 @@
         <v>896</v>
       </c>
       <c r="C13" t="s">
-        <v>910</v>
+        <v>848</v>
       </c>
       <c r="D13" t="s">
-        <v>833</v>
+        <v>849</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
         <v>834</v>
       </c>
       <c r="G13" t="s">
-        <v>911</v>
+        <v>850</v>
       </c>
       <c r="H13" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="I13">
-        <v>15.198</v>
+        <v>46.625</v>
       </c>
       <c r="J13">
-        <v>1470</v>
+        <v>4810</v>
       </c>
       <c r="K13">
-        <v>274</v>
+        <v>577</v>
       </c>
       <c r="L13">
-        <v>1744</v>
+        <v>5387</v>
       </c>
       <c r="M13">
-        <v>839</v>
+        <v>1542</v>
       </c>
       <c r="N13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O13" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="P13" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
       </c>
       <c r="S13" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="T13">
         <v>5</v>
       </c>
       <c r="U13" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -29595,7 +29534,7 @@
         <v>896</v>
       </c>
       <c r="C14" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="D14" t="s">
         <v>833</v>
@@ -29607,46 +29546,46 @@
         <v>834</v>
       </c>
       <c r="G14" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
       <c r="H14" t="s">
-        <v>919</v>
+        <v>912</v>
       </c>
       <c r="I14">
-        <v>3.3130000000000002</v>
+        <v>15.198</v>
       </c>
       <c r="J14">
-        <v>710</v>
+        <v>1470</v>
       </c>
       <c r="K14">
-        <v>14</v>
+        <v>274</v>
       </c>
       <c r="L14">
-        <v>724</v>
+        <v>1744</v>
       </c>
       <c r="M14">
-        <v>56</v>
+        <v>839</v>
       </c>
       <c r="N14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O14" t="s">
-        <v>920</v>
+        <v>913</v>
       </c>
       <c r="P14" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
       </c>
       <c r="S14" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
       <c r="T14">
         <v>5</v>
       </c>
       <c r="U14" t="s">
-        <v>923</v>
+        <v>916</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -29657,10 +29596,10 @@
         <v>896</v>
       </c>
       <c r="C15" t="s">
-        <v>924</v>
+        <v>917</v>
       </c>
       <c r="D15" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="E15" t="s">
         <v>31</v>
@@ -29669,46 +29608,46 @@
         <v>834</v>
       </c>
       <c r="G15" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="H15" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
       <c r="I15">
-        <v>14.625999999999999</v>
+        <v>3.3130000000000002</v>
       </c>
       <c r="J15">
-        <v>1346</v>
+        <v>710</v>
       </c>
       <c r="K15">
-        <v>237</v>
+        <v>14</v>
       </c>
       <c r="L15">
-        <v>1583</v>
+        <v>724</v>
       </c>
       <c r="M15">
-        <v>832</v>
+        <v>56</v>
       </c>
       <c r="N15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O15" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="P15" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="Q15" t="b">
         <v>1</v>
       </c>
       <c r="S15" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="T15">
         <v>5</v>
       </c>
       <c r="U15" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -29719,58 +29658,58 @@
         <v>896</v>
       </c>
       <c r="C16" t="s">
-        <v>657</v>
+        <v>924</v>
       </c>
       <c r="D16" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F16" t="s">
         <v>834</v>
       </c>
       <c r="G16" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="H16" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="I16">
-        <v>10.747</v>
+        <v>14.625999999999999</v>
       </c>
       <c r="J16">
-        <v>1095</v>
+        <v>1346</v>
       </c>
       <c r="K16">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="L16">
-        <v>1365</v>
+        <v>1583</v>
       </c>
       <c r="M16">
-        <v>725</v>
+        <v>832</v>
       </c>
       <c r="N16">
         <v>4</v>
       </c>
       <c r="O16" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="P16" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="Q16" t="b">
         <v>1</v>
       </c>
       <c r="S16" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="T16">
         <v>5</v>
       </c>
       <c r="U16" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -29781,58 +29720,58 @@
         <v>896</v>
       </c>
       <c r="C17" t="s">
-        <v>937</v>
+        <v>657</v>
       </c>
       <c r="D17" t="s">
         <v>849</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
         <v>834</v>
       </c>
       <c r="G17" t="s">
-        <v>938</v>
+        <v>931</v>
       </c>
       <c r="H17" t="s">
-        <v>939</v>
+        <v>932</v>
       </c>
       <c r="I17">
-        <v>14.574999999999999</v>
+        <v>10.747</v>
       </c>
       <c r="J17">
-        <v>1561</v>
+        <v>1095</v>
       </c>
       <c r="K17">
-        <v>190</v>
+        <v>270</v>
       </c>
       <c r="L17">
-        <v>1751</v>
+        <v>1365</v>
       </c>
       <c r="M17">
-        <v>607</v>
+        <v>725</v>
       </c>
       <c r="N17">
         <v>4</v>
       </c>
       <c r="O17" t="s">
-        <v>940</v>
+        <v>933</v>
       </c>
       <c r="P17" t="s">
-        <v>941</v>
+        <v>934</v>
       </c>
       <c r="Q17" t="b">
         <v>1</v>
       </c>
       <c r="S17" t="s">
-        <v>942</v>
+        <v>935</v>
       </c>
       <c r="T17">
         <v>5</v>
       </c>
       <c r="U17" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -29843,58 +29782,58 @@
         <v>896</v>
       </c>
       <c r="C18" t="s">
-        <v>856</v>
+        <v>937</v>
       </c>
       <c r="D18" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="E18" t="s">
-        <v>185</v>
+        <v>31</v>
       </c>
       <c r="F18" t="s">
-        <v>858</v>
+        <v>834</v>
       </c>
       <c r="G18" t="s">
-        <v>859</v>
+        <v>938</v>
       </c>
       <c r="H18" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="I18">
-        <v>12.265000000000001</v>
+        <v>14.574999999999999</v>
       </c>
       <c r="J18">
-        <v>1114</v>
+        <v>1561</v>
       </c>
       <c r="K18">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="L18">
-        <v>1224</v>
+        <v>1751</v>
       </c>
       <c r="M18">
-        <v>413</v>
+        <v>607</v>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O18" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="P18" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="Q18" t="b">
         <v>1</v>
       </c>
       <c r="S18" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="T18">
         <v>5</v>
       </c>
       <c r="U18" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -29905,7 +29844,7 @@
         <v>896</v>
       </c>
       <c r="C19" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="D19" t="s">
         <v>857</v>
@@ -29917,789 +29856,851 @@
         <v>858</v>
       </c>
       <c r="G19" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
       <c r="H19" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="I19">
-        <v>25.914000000000001</v>
+        <v>12.265000000000001</v>
       </c>
       <c r="J19">
-        <v>2294</v>
+        <v>1114</v>
       </c>
       <c r="K19">
-        <v>498</v>
+        <v>110</v>
       </c>
       <c r="L19">
-        <v>2792</v>
+        <v>1224</v>
       </c>
       <c r="M19">
-        <v>1500</v>
+        <v>413</v>
       </c>
       <c r="N19">
         <v>3</v>
       </c>
       <c r="O19" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="P19" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="Q19" t="b">
         <v>1</v>
       </c>
       <c r="S19" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="T19">
         <v>5</v>
       </c>
       <c r="U19" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="I20" s="4">
+        <v>25.914000000000001</v>
+      </c>
+      <c r="J20" s="4">
+        <v>2294</v>
+      </c>
+      <c r="K20" s="4">
+        <v>498</v>
+      </c>
+      <c r="L20" s="4">
+        <v>2792</v>
+      </c>
+      <c r="M20" s="4">
+        <v>1500</v>
+      </c>
+      <c r="N20" s="4">
+        <v>3</v>
+      </c>
+      <c r="O20" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="Q20" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="T20" s="4">
+        <v>5</v>
+      </c>
+      <c r="U20" s="4" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="21" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>895</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" s="4" t="s">
         <v>896</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D21" s="4" t="s">
         <v>857</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E21" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F21" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G21" s="4" t="s">
         <v>874</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H21" s="4" t="s">
         <v>954</v>
       </c>
-      <c r="I20">
+      <c r="I21" s="4">
         <v>12.736000000000001</v>
       </c>
-      <c r="J20">
+      <c r="J21" s="4">
         <v>1679</v>
       </c>
-      <c r="K20">
+      <c r="K21" s="4">
         <v>225</v>
       </c>
-      <c r="L20">
+      <c r="L21" s="4">
         <v>1904</v>
       </c>
-      <c r="M20">
+      <c r="M21" s="4">
         <v>767</v>
       </c>
-      <c r="N20">
+      <c r="N21" s="4">
         <v>4</v>
       </c>
-      <c r="O20" t="s">
+      <c r="O21" s="4" t="s">
         <v>955</v>
       </c>
-      <c r="P20" t="s">
+      <c r="P21" s="4" t="s">
         <v>956</v>
       </c>
-      <c r="Q20" t="b">
-        <v>1</v>
-      </c>
-      <c r="S20" t="s">
+      <c r="Q21" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S21" s="4" t="s">
         <v>957</v>
       </c>
-      <c r="T20">
+      <c r="T21" s="4">
         <v>5</v>
       </c>
-      <c r="U20" t="s">
+      <c r="U21" s="4" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="22" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
         <v>895</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" s="4" t="s">
         <v>896</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" s="4" t="s">
         <v>880</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D22" s="4" t="s">
         <v>857</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E22" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F22" s="4" t="s">
         <v>858</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G22" s="4" t="s">
         <v>881</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H22" s="4" t="s">
         <v>958</v>
       </c>
-      <c r="I21">
+      <c r="I22" s="4">
         <v>40.725000000000001</v>
       </c>
-      <c r="J21">
+      <c r="J22" s="4">
         <v>2887</v>
       </c>
-      <c r="K21">
+      <c r="K22" s="4">
         <v>865</v>
       </c>
-      <c r="L21">
+      <c r="L22" s="4">
         <v>3752</v>
       </c>
-      <c r="M21">
+      <c r="M22" s="4">
         <v>2428</v>
       </c>
-      <c r="N21">
+      <c r="N22" s="4">
         <v>5</v>
       </c>
-      <c r="O21" t="s">
+      <c r="O22" s="4" t="s">
         <v>959</v>
       </c>
-      <c r="P21" t="s">
+      <c r="P22" s="4" t="s">
         <v>960</v>
       </c>
-      <c r="Q21" t="b">
-        <v>1</v>
-      </c>
-      <c r="S21" t="s">
+      <c r="Q22" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S22" s="4" t="s">
         <v>961</v>
       </c>
-      <c r="T21">
+      <c r="T22" s="4">
         <v>4</v>
       </c>
-      <c r="U21" t="s">
+      <c r="U22" s="4" t="s">
         <v>962</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="23" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>895</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" s="4" t="s">
         <v>896</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C23" s="4" t="s">
         <v>887</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D23" s="4" t="s">
         <v>857</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E23" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F23" s="4" t="s">
         <v>888</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G23" s="4" t="s">
         <v>889</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H23" s="4" t="s">
         <v>963</v>
       </c>
-      <c r="I22">
+      <c r="I23" s="4">
         <v>32.576999999999998</v>
       </c>
-      <c r="J22">
+      <c r="J23" s="4">
         <v>3207</v>
       </c>
-      <c r="K22">
+      <c r="K23" s="4">
         <v>273</v>
       </c>
-      <c r="L22">
+      <c r="L23" s="4">
         <v>3480</v>
       </c>
-      <c r="M22">
+      <c r="M23" s="4">
         <v>905</v>
       </c>
-      <c r="N22">
+      <c r="N23" s="4">
         <v>3</v>
       </c>
-      <c r="O22" t="s">
+      <c r="O23" s="4" t="s">
         <v>891</v>
       </c>
-      <c r="P22" t="s">
+      <c r="P23" s="4" t="s">
         <v>964</v>
       </c>
-      <c r="Q22" t="b">
-        <v>1</v>
-      </c>
-      <c r="S22" t="s">
+      <c r="Q23" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="S23" s="4" t="s">
         <v>965</v>
       </c>
-      <c r="T22">
+      <c r="T23" s="4">
         <v>5</v>
       </c>
-      <c r="U22" t="s">
+      <c r="U23" s="4" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="24" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B24" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C24" s="2" t="s">
         <v>966</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D24" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E24" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F24" s="2" t="s">
         <v>858</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G24" s="2" t="s">
         <v>967</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H24" s="2" t="s">
         <v>968</v>
       </c>
-      <c r="I23">
+      <c r="I24" s="2">
         <v>38.002000000000002</v>
       </c>
-      <c r="J23">
+      <c r="J24" s="2">
         <v>2394</v>
       </c>
-      <c r="K23">
+      <c r="K24" s="2">
         <v>981</v>
       </c>
-      <c r="L23">
+      <c r="L24" s="2">
         <v>3375</v>
       </c>
-      <c r="M23">
+      <c r="M24" s="2">
         <v>2388</v>
       </c>
-      <c r="N23">
+      <c r="N24" s="2">
         <v>5</v>
       </c>
-      <c r="O23" t="s">
+      <c r="O24" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="P23" t="s">
+      <c r="P24" s="2" t="s">
         <v>970</v>
       </c>
-      <c r="Q23" t="b">
-        <v>1</v>
-      </c>
-      <c r="S23" t="s">
+      <c r="Q24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S24" s="2" t="s">
         <v>971</v>
       </c>
-      <c r="T23">
+      <c r="T24" s="2">
         <v>5</v>
       </c>
-      <c r="U23" t="s">
+      <c r="U24" s="2" t="s">
         <v>972</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="25" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C25" s="2" t="s">
         <v>973</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E25" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F25" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G25" s="2" t="s">
         <v>975</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H25" s="2" t="s">
         <v>976</v>
       </c>
-      <c r="I24">
+      <c r="I25" s="2">
         <v>8.6470000000000002</v>
       </c>
-      <c r="J24">
+      <c r="J25" s="2">
         <v>890</v>
       </c>
-      <c r="K24">
+      <c r="K25" s="2">
         <v>54</v>
       </c>
-      <c r="L24">
+      <c r="L25" s="2">
         <v>944</v>
       </c>
-      <c r="M24">
+      <c r="M25" s="2">
         <v>182</v>
       </c>
-      <c r="N24">
+      <c r="N25" s="2">
         <v>4</v>
       </c>
-      <c r="O24" t="s">
+      <c r="O25" s="2" t="s">
         <v>977</v>
       </c>
-      <c r="P24" t="s">
+      <c r="P25" s="2" t="s">
         <v>978</v>
       </c>
-      <c r="Q24" t="b">
-        <v>1</v>
-      </c>
-      <c r="S24" t="s">
+      <c r="Q25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S25" s="2" t="s">
         <v>979</v>
       </c>
-      <c r="T24">
+      <c r="T25" s="2">
         <v>3</v>
       </c>
-      <c r="U24" t="s">
+      <c r="U25" s="2" t="s">
         <v>980</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="26" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E26" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F26" s="2" t="s">
         <v>888</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G26" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H26" s="2" t="s">
         <v>983</v>
       </c>
-      <c r="I25">
+      <c r="I26" s="2">
         <v>14.48</v>
       </c>
-      <c r="J25">
+      <c r="J26" s="2">
         <v>1742</v>
       </c>
-      <c r="K25">
+      <c r="K26" s="2">
         <v>190</v>
       </c>
-      <c r="L25">
+      <c r="L26" s="2">
         <v>1932</v>
       </c>
-      <c r="M25">
+      <c r="M26" s="2">
         <v>840</v>
       </c>
-      <c r="N25">
+      <c r="N26" s="2">
         <v>4</v>
       </c>
-      <c r="O25" t="s">
+      <c r="O26" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="P25" t="s">
+      <c r="P26" s="2" t="s">
         <v>985</v>
       </c>
-      <c r="Q25" t="b">
-        <v>1</v>
-      </c>
-      <c r="S25" t="s">
+      <c r="Q26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S26" s="2" t="s">
         <v>986</v>
       </c>
-      <c r="T25">
+      <c r="T26" s="2">
         <v>5</v>
       </c>
-      <c r="U25" t="s">
+      <c r="U26" s="2" t="s">
         <v>987</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="27" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C27" s="2" t="s">
         <v>988</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E27" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F27" s="2" t="s">
         <v>858</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G27" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H27" s="2" t="s">
         <v>990</v>
       </c>
-      <c r="I26">
+      <c r="I27" s="2">
         <v>26.873000000000001</v>
       </c>
-      <c r="J26">
+      <c r="J27" s="2">
         <v>1994</v>
       </c>
-      <c r="K26">
+      <c r="K27" s="2">
         <v>456</v>
       </c>
-      <c r="L26">
+      <c r="L27" s="2">
         <v>2450</v>
       </c>
-      <c r="M26">
+      <c r="M27" s="2">
         <v>1315</v>
       </c>
-      <c r="N26">
+      <c r="N27" s="2">
         <v>4</v>
       </c>
-      <c r="O26" t="s">
+      <c r="O27" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="P26" t="s">
+      <c r="P27" s="2" t="s">
         <v>992</v>
       </c>
-      <c r="Q26" t="b">
-        <v>1</v>
-      </c>
-      <c r="S26" t="s">
+      <c r="Q27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S27" s="2" t="s">
         <v>993</v>
       </c>
-      <c r="T26">
+      <c r="T27" s="2">
         <v>4</v>
       </c>
-      <c r="U26" t="s">
+      <c r="U27" s="2" t="s">
         <v>994</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="28" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" s="2" t="s">
         <v>995</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E28" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F28" s="2" t="s">
         <v>996</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G28" s="2" t="s">
         <v>997</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H28" s="2" t="s">
         <v>998</v>
       </c>
-      <c r="I27">
+      <c r="I28" s="2">
         <v>39.655000000000001</v>
       </c>
-      <c r="J27">
+      <c r="J28" s="2">
         <v>4138</v>
       </c>
-      <c r="K27">
+      <c r="K28" s="2">
         <v>1032</v>
       </c>
-      <c r="L27">
+      <c r="L28" s="2">
         <v>5170</v>
       </c>
-      <c r="M27">
+      <c r="M28" s="2">
         <v>3729</v>
       </c>
-      <c r="N27">
+      <c r="N28" s="2">
         <v>5</v>
       </c>
-      <c r="O27" t="s">
+      <c r="O28" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="P27" t="s">
+      <c r="P28" s="2" t="s">
         <v>1000</v>
       </c>
-      <c r="Q27" t="b">
-        <v>1</v>
-      </c>
-      <c r="S27" t="s">
+      <c r="Q28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S28" s="2" t="s">
         <v>1001</v>
       </c>
-      <c r="T27">
+      <c r="T28" s="2">
         <v>5</v>
       </c>
-      <c r="U27" t="s">
+      <c r="U28" s="2" t="s">
         <v>1002</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="29" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C29" s="2" t="s">
         <v>1003</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E29" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F29" s="2" t="s">
         <v>888</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G29" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H29" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="I28">
+      <c r="I29" s="2">
         <v>15.651</v>
       </c>
-      <c r="J28">
+      <c r="J29" s="2">
         <v>1604</v>
       </c>
-      <c r="K28">
+      <c r="K29" s="2">
         <v>117</v>
       </c>
-      <c r="L28">
+      <c r="L29" s="2">
         <v>1721</v>
       </c>
-      <c r="M28">
+      <c r="M29" s="2">
         <v>454</v>
       </c>
-      <c r="N28">
+      <c r="N29" s="2">
         <v>5</v>
       </c>
-      <c r="O28" t="s">
+      <c r="O29" s="2" t="s">
         <v>1006</v>
       </c>
-      <c r="P28" t="s">
+      <c r="P29" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="Q28" t="b">
-        <v>1</v>
-      </c>
-      <c r="S28" t="s">
+      <c r="Q29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S29" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="T28">
+      <c r="T29" s="2">
         <v>3</v>
       </c>
-      <c r="U28" t="s">
+      <c r="U29" s="2" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="30" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C30" s="2" t="s">
         <v>1010</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E30" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F30" s="2" t="s">
         <v>858</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G30" s="2" t="s">
         <v>1011</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H30" s="2" t="s">
         <v>1012</v>
       </c>
-      <c r="I29">
+      <c r="I30" s="2">
         <v>55.259</v>
       </c>
-      <c r="J29">
+      <c r="J30" s="2">
         <v>4114</v>
       </c>
-      <c r="K29">
+      <c r="K30" s="2">
         <v>892</v>
       </c>
-      <c r="L29">
+      <c r="L30" s="2">
         <v>5006</v>
       </c>
-      <c r="M29">
+      <c r="M30" s="2">
         <v>3380</v>
       </c>
-      <c r="N29">
+      <c r="N30" s="2">
         <v>3</v>
       </c>
-      <c r="O29" t="s">
+      <c r="O30" s="2" t="s">
         <v>1013</v>
       </c>
-      <c r="P29" t="s">
+      <c r="P30" s="2" t="s">
         <v>1014</v>
       </c>
-      <c r="Q29" t="b">
-        <v>1</v>
-      </c>
-      <c r="S29" t="s">
+      <c r="Q30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S30" s="2" t="s">
         <v>1015</v>
       </c>
-      <c r="T29">
+      <c r="T30" s="2">
         <v>5</v>
       </c>
-      <c r="U29" t="s">
+      <c r="U30" s="2" t="s">
         <v>1016</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="31" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" s="2" t="s">
         <v>1017</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E31" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F31" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G31" s="2" t="s">
         <v>1018</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H31" s="2" t="s">
         <v>1019</v>
       </c>
-      <c r="I30">
+      <c r="I31" s="2">
         <v>37.305999999999997</v>
       </c>
-      <c r="J30">
+      <c r="J31" s="2">
         <v>2368</v>
       </c>
-      <c r="K30">
+      <c r="K31" s="2">
         <v>1077</v>
       </c>
-      <c r="L30">
+      <c r="L31" s="2">
         <v>3445</v>
       </c>
-      <c r="M30">
+      <c r="M31" s="2">
         <v>2722</v>
       </c>
-      <c r="N30">
+      <c r="N31" s="2">
         <v>2</v>
       </c>
-      <c r="O30" t="s">
+      <c r="O31" s="2" t="s">
         <v>1020</v>
       </c>
-      <c r="P30" t="s">
+      <c r="P31" s="2" t="s">
         <v>1021</v>
       </c>
-      <c r="Q30" t="b">
-        <v>1</v>
-      </c>
-      <c r="S30" t="s">
+      <c r="Q31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S31" s="2" t="s">
         <v>1022</v>
       </c>
-      <c r="T30">
+      <c r="T31" s="2">
         <v>5</v>
       </c>
-      <c r="U30" t="s">
+      <c r="U31" s="2" t="s">
         <v>1023</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="32" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C32" s="2" t="s">
         <v>1024</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D32" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E32" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F32" s="2" t="s">
         <v>996</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G32" s="2" t="s">
         <v>1025</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H32" s="2" t="s">
         <v>1026</v>
       </c>
-      <c r="I31">
+      <c r="I32" s="2">
         <v>49.478999999999999</v>
       </c>
-      <c r="J31">
+      <c r="J32" s="2">
         <v>6759</v>
       </c>
-      <c r="K31">
+      <c r="K32" s="2">
         <v>1046</v>
       </c>
-      <c r="L31">
+      <c r="L32" s="2">
         <v>7805</v>
       </c>
-      <c r="M31">
+      <c r="M32" s="2">
         <v>2912</v>
       </c>
-      <c r="N31">
+      <c r="N32" s="2">
         <v>5</v>
       </c>
-      <c r="O31" t="s">
+      <c r="O32" s="2" t="s">
         <v>1027</v>
       </c>
-      <c r="P31" t="s">
+      <c r="P32" s="2" t="s">
         <v>1028</v>
       </c>
-      <c r="Q31" t="b">
-        <v>1</v>
-      </c>
-      <c r="S31" t="s">
+      <c r="Q32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S32" s="2" t="s">
         <v>1029</v>
       </c>
-      <c r="T31">
+      <c r="T32" s="2">
         <v>5</v>
       </c>
-      <c r="U31" t="s">
+      <c r="U32" s="2" t="s">
         <v>1030</v>
       </c>
     </row>

--- a/benchmark_results.xlsx
+++ b/benchmark_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AALB\Desktop\mp\graph\graphxmaf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C4ACC2-B0B4-4BE7-9B20-0CB32EA1F032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC88BE38-169A-4920-BDC8-76D5642B8C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Graph" sheetId="1" r:id="rId1"/>
@@ -48220,7 +48220,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="80" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="142" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="56" customWidth="1"/>

--- a/benchmark_results.xlsx
+++ b/benchmark_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AALB\Desktop\mp\graph\graphxmaf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC88BE38-169A-4920-BDC8-76D5642B8C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7762B742-1584-47FA-AD0A-07563730041B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3255" yWindow="5640" windowWidth="28800" windowHeight="15345" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Graph" sheetId="1" r:id="rId1"/>
@@ -54186,7 +54186,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -55232,6 +55232,12 @@
         <v>1770</v>
       </c>
     </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J32">
+        <f>AVERAGE(J23:J26)</f>
+        <v>3.915</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
